--- a/Cleaned Data/Sellers.xlsx
+++ b/Cleaned Data/Sellers.xlsx
@@ -8,12 +8,12 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Amit Diploma\Olist-ECommerce-Insights-End-to-End-Data-Analysis\Cleaned Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EE25381A-46D5-4A4D-B0A8-6D028CACB37C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3332558D-326A-45D8-9987-2738DF41C41E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sellers" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
